--- a/Assignments/Excel_Assignment/Assignment Data_QUESTIONS/VLOOKUP 2a.xlsx
+++ b/Assignments/Excel_Assignment/Assignment Data_QUESTIONS/VLOOKUP 2a.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20397"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Janvi\Desktop\Excel Exercise\Excel Practice WorkBook\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UMA SURYAVANSHI\Desktop\Tops_Tech\Assignments\Excel_Assignment\Assignment Data_QUESTIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF54AEA-EE11-436C-8EAD-495770360852}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87B1184-EB13-4DC4-854F-38D1F54FECCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10425" xr2:uid="{49AE84F3-0EE5-47A4-BC2B-AA7920376694}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{49AE84F3-0EE5-47A4-BC2B-AA7920376694}"/>
   </bookViews>
   <sheets>
     <sheet name="VLOOUP 2A Questions" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
   <si>
     <t>VLOOKUP Exercise - Data:</t>
   </si>
@@ -109,9 +109,6 @@
   </si>
   <si>
     <t>Questions</t>
-  </si>
-  <si>
-    <t>s</t>
   </si>
   <si>
     <t>Create a VLOOKUP formula to find the occupation of Jane Doe.</t>
@@ -542,22 +539,22 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:K49"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.7109375" style="2"/>
+    <col min="1" max="1" width="2.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
@@ -571,7 +568,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
@@ -585,7 +582,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
@@ -599,7 +596,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
@@ -613,7 +610,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
@@ -627,7 +624,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>15</v>
       </c>
@@ -641,7 +638,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
@@ -655,7 +652,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>19</v>
       </c>
@@ -669,7 +666,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>21</v>
       </c>
@@ -683,7 +680,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>23</v>
       </c>
@@ -697,7 +694,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>25</v>
       </c>
@@ -711,37 +708,32 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="G16" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>1</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C18" s="6" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="C18" s="6" t="s">
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="6"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B19" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="C19" s="7"/>
     </row>
-    <row r="20" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
@@ -753,7 +745,7 @@
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
     </row>
-    <row r="21" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
@@ -765,7 +757,7 @@
       <c r="J21" s="8"/>
       <c r="K21" s="8"/>
     </row>
-    <row r="22" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -777,7 +769,7 @@
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
     </row>
-    <row r="23" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -789,7 +781,7 @@
       <c r="J23" s="8"/>
       <c r="K23" s="8"/>
     </row>
-    <row r="24" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -801,7 +793,7 @@
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
     </row>
-    <row r="25" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
@@ -813,7 +805,7 @@
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
     </row>
-    <row r="26" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
@@ -825,28 +817,28 @@
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
     </row>
-    <row r="27" spans="1:11" collapsed="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" collapsed="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>2</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C29" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" s="6"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B30" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="6"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B30" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="C30" s="7"/>
     </row>
-    <row r="31" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -858,7 +850,7 @@
       <c r="J31" s="8"/>
       <c r="K31" s="8"/>
     </row>
-    <row r="32" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -870,7 +862,7 @@
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
     </row>
-    <row r="33" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -882,7 +874,7 @@
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
     </row>
-    <row r="34" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -894,7 +886,7 @@
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
     </row>
-    <row r="35" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -906,7 +898,7 @@
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
     </row>
-    <row r="36" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -918,7 +910,7 @@
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
     </row>
-    <row r="37" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
@@ -930,28 +922,28 @@
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
     </row>
-    <row r="38" spans="1:11" collapsed="1" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" collapsed="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>2</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C40" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40" s="6"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D40" s="6"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B41" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="C41" s="7"/>
     </row>
-    <row r="42" spans="1:11" ht="12.95" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" ht="13" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
@@ -963,7 +955,7 @@
       <c r="J42" s="8"/>
       <c r="K42" s="8"/>
     </row>
-    <row r="43" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
@@ -975,7 +967,7 @@
       <c r="J43" s="8"/>
       <c r="K43" s="8"/>
     </row>
-    <row r="44" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
@@ -987,7 +979,7 @@
       <c r="J44" s="8"/>
       <c r="K44" s="8"/>
     </row>
-    <row r="45" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
@@ -999,7 +991,7 @@
       <c r="J45" s="8"/>
       <c r="K45" s="8"/>
     </row>
-    <row r="46" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
@@ -1011,7 +1003,7 @@
       <c r="J46" s="8"/>
       <c r="K46" s="8"/>
     </row>
-    <row r="47" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
@@ -1023,7 +1015,7 @@
       <c r="J47" s="8"/>
       <c r="K47" s="8"/>
     </row>
-    <row r="48" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
@@ -1035,7 +1027,7 @@
       <c r="J48" s="8"/>
       <c r="K48" s="8"/>
     </row>
-    <row r="49" collapsed="1" x14ac:dyDescent="0.2"/>
+    <row r="49" collapsed="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B20:K26"/>
